--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-14).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-14).xlsx
@@ -915,66 +915,66 @@
   </si>
   <si>
     <t>215
-145</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>R$ 655.442,10</t>
-  </si>
-  <si>
-    <t>R$ 4.148,37
-R$ 4.306,94</t>
+168</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>R$ 737.898,31</t>
+  </si>
+  <si>
+    <t>R$ 4.054,39
+R$ 4.196,22</t>
   </si>
   <si>
     <t>(11.4%)
-(8.0%)</t>
-  </si>
-  <si>
-    <t>45.5</t>
-  </si>
-  <si>
-    <t>(15.6%)</t>
-  </si>
-  <si>
-    <t>66.9%</t>
-  </si>
-  <si>
-    <t>27.1%</t>
-  </si>
-  <si>
-    <t>3.5%</t>
-  </si>
-  <si>
-    <t>(0.1%)</t>
-  </si>
-  <si>
-    <t>25.7</t>
-  </si>
-  <si>
-    <t>73.9%</t>
-  </si>
-  <si>
-    <t>7.6%</t>
-  </si>
-  <si>
-    <t>4.6</t>
-  </si>
-  <si>
-    <t>6.6</t>
-  </si>
-  <si>
-    <t>11.1</t>
-  </si>
-  <si>
-    <t>17.8</t>
-  </si>
-  <si>
-    <t>75.5%</t>
-  </si>
-  <si>
-    <t>-R$ 13.158,27</t>
+(8.6%)</t>
+  </si>
+  <si>
+    <t>44.7</t>
+  </si>
+  <si>
+    <t>(15.9%)</t>
+  </si>
+  <si>
+    <t>69.8%</t>
+  </si>
+  <si>
+    <t>28.0%</t>
+  </si>
+  <si>
+    <t>3.9%</t>
+  </si>
+  <si>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>26.2</t>
+  </si>
+  <si>
+    <t>72.8%</t>
+  </si>
+  <si>
+    <t>8.2%</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>6.9</t>
+  </si>
+  <si>
+    <t>11.4</t>
+  </si>
+  <si>
+    <t>18.0</t>
+  </si>
+  <si>
+    <t>74.4%</t>
+  </si>
+  <si>
+    <t>-R$ 15.136,65</t>
   </si>
   <si>
     <t>2.94</t>
@@ -1414,7 +1414,7 @@
     <col min="14" max="14" width="12.14" customWidth="1"/>
     <col min="15" max="15" width="15.29" customWidth="1"/>
     <col min="16" max="16" width="16" customWidth="1"/>
-    <col min="17" max="17" width="6.86" customWidth="1"/>
+    <col min="17" max="17" width="7.71" customWidth="1"/>
     <col min="18" max="18" width="10.14" customWidth="1"/>
     <col min="19" max="19" width="13.71" customWidth="1"/>
     <col min="20" max="20" width="12" customWidth="1"/>
@@ -2349,10 +2349,10 @@
         <v>0.1964285714285714</v>
       </c>
       <c r="T8" s="6">
-        <v>0.36005632560183404</v>
+        <v>0.36497864157704873</v>
       </c>
       <c r="U8" s="6">
-        <v>0.017887236383579565</v>
+        <v>0.022809552358794255</v>
       </c>
       <c r="V8" s="6">
         <v>0.040005569540913131</v>
@@ -3289,7 +3289,7 @@
         <v>3.6589638655462182</v>
       </c>
       <c r="AC15" s="8">
-        <v>9.0652179999999998</v>
+        <v>9.0326540000000008</v>
       </c>
       <c r="AD15" s="8">
         <v>15.9315275</v>
@@ -4615,7 +4615,7 @@
         <v>19540</v>
       </c>
       <c r="B26" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C26" s="4">
         <v>44</v>
@@ -4651,25 +4651,61 @@
       <c t="s" r="N26" s="4">
         <v>52</v>
       </c>
-      <c r="O26" s="5"/>
-      <c r="P26" s="5"/>
-      <c r="Q26" s="6"/>
-      <c r="R26" s="7"/>
-      <c r="S26" s="6"/>
-      <c r="T26" s="6"/>
-      <c r="U26" s="6"/>
-      <c r="V26" s="6"/>
-      <c r="W26" s="6"/>
-      <c r="X26" s="8"/>
-      <c r="Y26" s="6"/>
-      <c r="Z26" s="6"/>
-      <c r="AA26" s="8"/>
-      <c r="AB26" s="8"/>
-      <c r="AC26" s="8"/>
-      <c r="AD26" s="8"/>
-      <c r="AE26" s="6"/>
+      <c r="O26" s="5">
+        <v>8829.5799999999999</v>
+      </c>
+      <c r="P26" s="5">
+        <v>8829.5799999999999</v>
+      </c>
+      <c r="Q26" s="6">
+        <v>-0.22560110859202676</v>
+      </c>
+      <c r="R26" s="7">
+        <v>86</v>
+      </c>
+      <c r="S26" s="6">
+        <v>-0.28925619834710747</v>
+      </c>
+      <c r="T26" s="6">
+        <v>0.35057547471114142</v>
+      </c>
+      <c r="U26" s="6">
+        <v>0.024025400981700147</v>
+      </c>
+      <c r="V26" s="6">
+        <v>0.038349728979181347</v>
+      </c>
+      <c r="W26" s="6">
+        <v>0.013512760516355251</v>
+      </c>
+      <c r="X26" s="8">
+        <v>23.119999999999997</v>
+      </c>
+      <c r="Y26" s="6">
+        <v>0.92727272727272725</v>
+      </c>
+      <c r="Z26" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="8">
+        <v>3.0263708860759495</v>
+      </c>
+      <c r="AB26" s="8">
+        <v>5.6789999999999994</v>
+      </c>
+      <c r="AC26" s="8">
+        <v>8.7305430000000008</v>
+      </c>
+      <c r="AD26" s="8">
+        <v>14.490303636363635</v>
+      </c>
+      <c r="AE26" s="6">
+        <v>0.87272727272727268</v>
+      </c>
       <c r="AF26" s="9"/>
-      <c r="AG26" s="5"/>
+      <c r="AG26" s="5">
+        <v>-363.82999999999998</v>
+      </c>
       <c r="AH26" s="10">
         <v>3</v>
       </c>
@@ -4841,7 +4877,7 @@
         <v>19546</v>
       </c>
       <c r="B28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C28" s="4">
         <v>44</v>
@@ -4877,25 +4913,61 @@
       <c t="s" r="N28" s="4">
         <v>52</v>
       </c>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="7"/>
-      <c r="S28" s="6"/>
-      <c r="T28" s="6"/>
-      <c r="U28" s="6"/>
-      <c r="V28" s="6"/>
-      <c r="W28" s="6"/>
-      <c r="X28" s="8"/>
-      <c r="Y28" s="6"/>
-      <c r="Z28" s="6"/>
-      <c r="AA28" s="8"/>
-      <c r="AB28" s="8"/>
-      <c r="AC28" s="8"/>
-      <c r="AD28" s="8"/>
-      <c r="AE28" s="6"/>
+      <c r="O28" s="5">
+        <v>2614.29</v>
+      </c>
+      <c r="P28" s="5">
+        <v>2614.29</v>
+      </c>
+      <c r="Q28" s="6">
+        <v>-0.43993101675307433</v>
+      </c>
+      <c r="R28" s="7">
+        <v>31</v>
+      </c>
+      <c r="S28" s="6">
+        <v>-0.41509433962264153</v>
+      </c>
+      <c r="T28" s="6">
+        <v>0.00070286770021688483</v>
+      </c>
+      <c r="U28" s="6">
+        <v>-0.32043977523534112</v>
+      </c>
+      <c r="V28" s="6">
+        <v>0.15262901208358676</v>
+      </c>
+      <c r="W28" s="6">
+        <v>0.13706838185511172</v>
+      </c>
+      <c r="X28" s="8">
+        <v>25.605882352941176</v>
+      </c>
+      <c r="Y28" s="6">
+        <v>0.76470588235294112</v>
+      </c>
+      <c r="Z28" s="6">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="AA28" s="8">
+        <v>2.6397838709677419</v>
+      </c>
+      <c r="AB28" s="8">
+        <v>9.485294117647058</v>
+      </c>
+      <c r="AC28" s="8">
+        <v>11.926034</v>
+      </c>
+      <c r="AD28" s="8">
+        <v>18.686276470588236</v>
+      </c>
+      <c r="AE28" s="6">
+        <v>0.76470588235294112</v>
+      </c>
       <c r="AF28" s="9"/>
-      <c r="AG28" s="5"/>
+      <c r="AG28" s="5">
+        <v>-232.25</v>
+      </c>
       <c r="AH28" s="10">
         <v>2</v>
       </c>
@@ -5587,7 +5659,7 @@
         <v>19560</v>
       </c>
       <c r="B34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C34" s="4">
         <v>44</v>
@@ -5623,25 +5695,61 @@
       <c t="s" r="N34" s="4">
         <v>52</v>
       </c>
-      <c r="O34" s="5"/>
-      <c r="P34" s="5"/>
-      <c r="Q34" s="6"/>
-      <c r="R34" s="7"/>
-      <c r="S34" s="6"/>
-      <c r="T34" s="6"/>
-      <c r="U34" s="6"/>
-      <c r="V34" s="6"/>
-      <c r="W34" s="6"/>
-      <c r="X34" s="8"/>
-      <c r="Y34" s="6"/>
-      <c r="Z34" s="6"/>
-      <c r="AA34" s="8"/>
-      <c r="AB34" s="8"/>
-      <c r="AC34" s="8"/>
-      <c r="AD34" s="8"/>
-      <c r="AE34" s="6"/>
+      <c r="O34" s="5">
+        <v>6771.4499999999998</v>
+      </c>
+      <c r="P34" s="5">
+        <v>6771.4499999999998</v>
+      </c>
+      <c r="Q34" s="6">
+        <v>-0.20691464504439516</v>
+      </c>
+      <c r="R34" s="7">
+        <v>69</v>
+      </c>
+      <c r="S34" s="6">
+        <v>-0.31683168316831678</v>
+      </c>
+      <c r="T34" s="6">
+        <v>0.28213252700677111</v>
+      </c>
+      <c r="U34" s="6">
+        <v>-0.045947869363282601</v>
+      </c>
+      <c r="V34" s="6">
+        <v>0.06868484593403186</v>
+      </c>
+      <c r="W34" s="6">
+        <v>0.027138352937701674</v>
+      </c>
+      <c r="X34" s="8">
+        <v>19.381667499999999</v>
+      </c>
+      <c r="Y34" s="6">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="Z34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="8">
+        <v>3.439613043478261</v>
+      </c>
+      <c r="AB34" s="8">
+        <v>2.3951763157894739</v>
+      </c>
+      <c r="AC34" s="8">
+        <v>7.0809470000000001</v>
+      </c>
+      <c r="AD34" s="8">
+        <v>12.840417500000001</v>
+      </c>
+      <c r="AE34" s="6">
+        <v>0.97499999999999998</v>
+      </c>
       <c r="AF34" s="9"/>
-      <c r="AG34" s="5"/>
+      <c r="AG34" s="5">
+        <v>0</v>
+      </c>
       <c r="AH34" s="10">
         <v>4</v>
       </c>
@@ -5895,7 +6003,9 @@
       <c r="AB36" s="8">
         <v>4.7204545454545448</v>
       </c>
-      <c r="AC36" s="8"/>
+      <c r="AC36" s="8">
+        <v>8.4954540000000005</v>
+      </c>
       <c r="AD36" s="8">
         <v>15.447727272727274</v>
       </c>
@@ -6077,7 +6187,7 @@
         <v>19564</v>
       </c>
       <c r="B38" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C38" s="4">
         <v>44</v>
@@ -6113,25 +6223,61 @@
       <c t="s" r="N38" s="4">
         <v>52</v>
       </c>
-      <c r="O38" s="5"/>
-      <c r="P38" s="5"/>
-      <c r="Q38" s="6"/>
-      <c r="R38" s="7"/>
-      <c r="S38" s="6"/>
-      <c r="T38" s="6"/>
-      <c r="U38" s="6"/>
-      <c r="V38" s="6"/>
-      <c r="W38" s="6"/>
-      <c r="X38" s="8"/>
-      <c r="Y38" s="6"/>
-      <c r="Z38" s="6"/>
-      <c r="AA38" s="8"/>
-      <c r="AB38" s="8"/>
-      <c r="AC38" s="8"/>
-      <c r="AD38" s="8"/>
-      <c r="AE38" s="6"/>
+      <c r="O38" s="5">
+        <v>3437.5</v>
+      </c>
+      <c r="P38" s="5">
+        <v>3437.5</v>
+      </c>
+      <c r="Q38" s="6">
+        <v>0.47399339650958372</v>
+      </c>
+      <c r="R38" s="7">
+        <v>46</v>
+      </c>
+      <c r="S38" s="6">
+        <v>0.76923076923076916</v>
+      </c>
+      <c r="T38" s="6">
+        <v>0.31188485818181816</v>
+      </c>
+      <c r="U38" s="6">
+        <v>-0.040807505454545458</v>
+      </c>
+      <c r="V38" s="6">
+        <v>0.025214836363636365</v>
+      </c>
+      <c r="W38" s="6">
+        <v>-0.013272436363636364</v>
+      </c>
+      <c r="X38" s="8">
+        <v>32.179032258064517</v>
+      </c>
+      <c r="Y38" s="6">
+        <v>0.67741935483870963</v>
+      </c>
+      <c r="Z38" s="6">
+        <v>0.22580645161290322</v>
+      </c>
+      <c r="AA38" s="8">
+        <v>4.0404755102040824</v>
+      </c>
+      <c r="AB38" s="8">
+        <v>9.3268806451612907</v>
+      </c>
+      <c r="AC38" s="8">
+        <v>13.396072</v>
+      </c>
+      <c r="AD38" s="8">
+        <v>20.166667741935484</v>
+      </c>
+      <c r="AE38" s="6">
+        <v>0.4838709677419355</v>
+      </c>
       <c r="AF38" s="9"/>
-      <c r="AG38" s="5"/>
+      <c r="AG38" s="5">
+        <v>0</v>
+      </c>
       <c r="AH38" s="10">
         <v>1</v>
       </c>
@@ -6172,7 +6318,7 @@
         <v>19565</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C39" s="4">
         <v>44</v>
@@ -6208,25 +6354,61 @@
       <c t="s" r="N39" s="4">
         <v>52</v>
       </c>
-      <c r="O39" s="5"/>
-      <c r="P39" s="5"/>
-      <c r="Q39" s="6"/>
-      <c r="R39" s="7"/>
-      <c r="S39" s="6"/>
-      <c r="T39" s="6"/>
-      <c r="U39" s="6"/>
-      <c r="V39" s="6"/>
-      <c r="W39" s="6"/>
-      <c r="X39" s="8"/>
-      <c r="Y39" s="6"/>
-      <c r="Z39" s="6"/>
-      <c r="AA39" s="8"/>
-      <c r="AB39" s="8"/>
-      <c r="AC39" s="8"/>
-      <c r="AD39" s="8"/>
-      <c r="AE39" s="6"/>
+      <c r="O39" s="5">
+        <v>3987.9000000000001</v>
+      </c>
+      <c r="P39" s="5">
+        <v>3987.9000000000001</v>
+      </c>
+      <c r="Q39" s="6">
+        <v>0.15472150476609658</v>
+      </c>
+      <c r="R39" s="7">
+        <v>47</v>
+      </c>
+      <c r="S39" s="6">
+        <v>0.14634146341463405</v>
+      </c>
+      <c r="T39" s="6">
+        <v>0.28751034378996465</v>
+      </c>
+      <c r="U39" s="6">
+        <v>-0.039007372301211166</v>
+      </c>
+      <c r="V39" s="6">
+        <v>0.083685774467764984</v>
+      </c>
+      <c r="W39" s="6">
+        <v>0.03460731211916046</v>
+      </c>
+      <c r="X39" s="8">
+        <v>21.930209375</v>
+      </c>
+      <c r="Y39" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z39" s="6">
+        <v>0.03125</v>
+      </c>
+      <c r="AA39" s="8">
+        <v>2.9192021739130434</v>
+      </c>
+      <c r="AB39" s="8">
+        <v>6.5827148148148149</v>
+      </c>
+      <c r="AC39" s="8">
+        <v>9.6655280000000001</v>
+      </c>
+      <c r="AD39" s="8">
+        <v>16.177603125000001</v>
+      </c>
+      <c r="AE39" s="6">
+        <v>0.84375</v>
+      </c>
       <c r="AF39" s="9"/>
-      <c r="AG39" s="5"/>
+      <c r="AG39" s="5">
+        <v>0</v>
+      </c>
       <c r="AH39" s="10">
         <v>4</v>
       </c>
@@ -6529,7 +6711,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6565,25 +6747,61 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
-      <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="O42" s="5">
+        <v>3350.9000000000001</v>
+      </c>
+      <c r="P42" s="5">
+        <v>3350.9000000000001</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>0.41997516770275833</v>
+      </c>
+      <c r="R42" s="7">
+        <v>42</v>
+      </c>
+      <c r="S42" s="6">
+        <v>0.61538461538461542</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.28499626965889763</v>
+      </c>
+      <c r="U42" s="6">
+        <v>-0.0038276283983407445</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.060974961950520754</v>
+      </c>
+      <c r="W42" s="6">
+        <v>-0.00054880778298367606</v>
+      </c>
+      <c r="X42" s="8">
+        <v>34.703470833333334</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>5.9594025641025636</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>11.828260869565218</v>
+      </c>
+      <c r="AC42" s="8">
+        <v>18.706731999999999</v>
+      </c>
+      <c r="AD42" s="8">
+        <v>24.981249999999999</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0.41666666666666669</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>0</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -6834,7 +7052,7 @@
         <v>5.7511099999999997</v>
       </c>
       <c r="AC44" s="8">
-        <v>9.1375139999999995</v>
+        <v>9.1276060000000001</v>
       </c>
       <c r="AD44" s="8">
         <v>15.210086842105262</v>
@@ -7535,7 +7753,7 @@
         <v>19601</v>
       </c>
       <c r="B50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C50" s="4">
         <v>44</v>
@@ -7571,25 +7789,61 @@
       <c t="s" r="N50" s="4">
         <v>52</v>
       </c>
-      <c r="O50" s="5"/>
-      <c r="P50" s="5"/>
-      <c r="Q50" s="6"/>
-      <c r="R50" s="7"/>
-      <c r="S50" s="6"/>
-      <c r="T50" s="6"/>
-      <c r="U50" s="6"/>
-      <c r="V50" s="6"/>
-      <c r="W50" s="6"/>
-      <c r="X50" s="8"/>
-      <c r="Y50" s="6"/>
-      <c r="Z50" s="6"/>
-      <c r="AA50" s="8"/>
-      <c r="AB50" s="8"/>
-      <c r="AC50" s="8"/>
-      <c r="AD50" s="8"/>
-      <c r="AE50" s="6"/>
+      <c r="O50" s="5">
+        <v>5361.4399999999996</v>
+      </c>
+      <c r="P50" s="5">
+        <v>5361.4399999999996</v>
+      </c>
+      <c r="Q50" s="6">
+        <v>0.41593182112288085</v>
+      </c>
+      <c r="R50" s="7">
+        <v>62</v>
+      </c>
+      <c r="S50" s="6">
+        <v>0.37777777777777777</v>
+      </c>
+      <c r="T50" s="6">
+        <v>0.18629828926557046</v>
+      </c>
+      <c r="U50" s="6">
+        <v>-0.13180281789966877</v>
+      </c>
+      <c r="V50" s="6">
+        <v>0.082821965740547329</v>
+      </c>
+      <c r="W50" s="6">
+        <v>0.038468210033125436</v>
+      </c>
+      <c r="X50" s="8">
+        <v>20.961905714285713</v>
+      </c>
+      <c r="Y50" s="6">
+        <v>0.88571428571428568</v>
+      </c>
+      <c r="Z50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="8">
+        <v>2.6754545454545458</v>
+      </c>
+      <c r="AB50" s="8">
+        <v>4.3901031250000004</v>
+      </c>
+      <c r="AC50" s="8">
+        <v>7.2382520000000001</v>
+      </c>
+      <c r="AD50" s="8">
+        <v>14.416665714285715</v>
+      </c>
+      <c r="AE50" s="6">
+        <v>0.97142857142857142</v>
+      </c>
       <c r="AF50" s="9"/>
-      <c r="AG50" s="5"/>
+      <c r="AG50" s="5">
+        <v>0</v>
+      </c>
       <c r="AH50" s="10">
         <v>4</v>
       </c>
@@ -7933,7 +8187,7 @@
         <v>2.7074055555555554</v>
       </c>
       <c r="AC53" s="8">
-        <v>5.5901949999999996</v>
+        <v>5.841666</v>
       </c>
       <c r="AD53" s="8">
         <v>12.771294444444443</v>
@@ -8116,7 +8370,7 @@
         <v>19615</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>44</v>
@@ -8152,25 +8406,61 @@
       <c t="s" r="N55" s="4">
         <v>52</v>
       </c>
-      <c r="O55" s="5"/>
-      <c r="P55" s="5"/>
-      <c r="Q55" s="6"/>
-      <c r="R55" s="7"/>
-      <c r="S55" s="6"/>
-      <c r="T55" s="6"/>
-      <c r="U55" s="6"/>
-      <c r="V55" s="6"/>
-      <c r="W55" s="6"/>
-      <c r="X55" s="8"/>
-      <c r="Y55" s="6"/>
-      <c r="Z55" s="6"/>
-      <c r="AA55" s="8"/>
-      <c r="AB55" s="8"/>
-      <c r="AC55" s="8"/>
-      <c r="AD55" s="8"/>
-      <c r="AE55" s="6"/>
+      <c r="O55" s="5">
+        <v>4249.4099999999999</v>
+      </c>
+      <c r="P55" s="5">
+        <v>4249.4099999999999</v>
+      </c>
+      <c r="Q55" s="6">
+        <v>0.02320468861364211</v>
+      </c>
+      <c r="R55" s="7">
+        <v>58</v>
+      </c>
+      <c r="S55" s="6">
+        <v>0.13725490196078427</v>
+      </c>
+      <c r="T55" s="6">
+        <v>-0.00060949637714412122</v>
+      </c>
+      <c r="U55" s="6">
+        <v>-0.35541404571458157</v>
+      </c>
+      <c r="V55" s="6">
+        <v>0.048935734607863213</v>
+      </c>
+      <c r="W55" s="6">
+        <v>0.016161773046140523</v>
+      </c>
+      <c r="X55" s="8">
+        <v>57.038636363636357</v>
+      </c>
+      <c r="Y55" s="6">
+        <v>0.022727272727272728</v>
+      </c>
+      <c r="Z55" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="AA55" s="8">
+        <v>2.598360655737705</v>
+      </c>
+      <c r="AB55" s="8">
+        <v>28.924243181818181</v>
+      </c>
+      <c r="AC55" s="8">
+        <v>31.583130000000001</v>
+      </c>
+      <c r="AD55" s="8">
+        <v>38.481818181818184</v>
+      </c>
+      <c r="AE55" s="6">
+        <v>0.022727272727272728</v>
+      </c>
       <c r="AF55" s="9"/>
-      <c r="AG55" s="5"/>
+      <c r="AG55" s="5">
+        <v>0</v>
+      </c>
       <c r="AH55" s="10">
         <v>2</v>
       </c>
@@ -8697,7 +8987,7 @@
         <v>19623</v>
       </c>
       <c r="B60" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C60" s="4">
         <v>44</v>
@@ -8733,25 +9023,53 @@
       <c t="s" r="N60" s="4">
         <v>52</v>
       </c>
-      <c r="O60" s="5"/>
-      <c r="P60" s="5"/>
-      <c r="Q60" s="6"/>
-      <c r="R60" s="7"/>
-      <c r="S60" s="6"/>
+      <c r="O60" s="5">
+        <v>0</v>
+      </c>
+      <c r="P60" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R60" s="7">
+        <v>25</v>
+      </c>
+      <c r="S60" s="6">
+        <v>-0.26470588235294112</v>
+      </c>
       <c r="T60" s="6"/>
       <c r="U60" s="6"/>
       <c r="V60" s="6"/>
       <c r="W60" s="6"/>
-      <c r="X60" s="8"/>
-      <c r="Y60" s="6"/>
-      <c r="Z60" s="6"/>
-      <c r="AA60" s="8"/>
-      <c r="AB60" s="8"/>
-      <c r="AC60" s="8"/>
-      <c r="AD60" s="8"/>
-      <c r="AE60" s="6"/>
+      <c r="X60" s="8">
+        <v>26.664705882352941</v>
+      </c>
+      <c r="Y60" s="6">
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="Z60" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="8">
+        <v>2.5209888888888887</v>
+      </c>
+      <c r="AB60" s="8">
+        <v>5.2312500000000002</v>
+      </c>
+      <c r="AC60" s="8">
+        <v>7.8886570000000003</v>
+      </c>
+      <c r="AD60" s="8">
+        <v>15.083335294117646</v>
+      </c>
+      <c r="AE60" s="6">
+        <v>0.82352941176470584</v>
+      </c>
       <c r="AF60" s="9"/>
-      <c r="AG60" s="5"/>
+      <c r="AG60" s="5">
+        <v>0</v>
+      </c>
       <c r="AH60" s="10">
         <v>4</v>
       </c>
@@ -9919,7 +10237,7 @@
         <v>19648</v>
       </c>
       <c r="B70" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C70" s="4">
         <v>44</v>
@@ -9955,25 +10273,61 @@
       <c t="s" r="N70" s="4">
         <v>52</v>
       </c>
-      <c r="O70" s="5"/>
-      <c r="P70" s="5"/>
-      <c r="Q70" s="6"/>
-      <c r="R70" s="7"/>
-      <c r="S70" s="6"/>
-      <c r="T70" s="6"/>
-      <c r="U70" s="6"/>
-      <c r="V70" s="6"/>
-      <c r="W70" s="6"/>
-      <c r="X70" s="8"/>
-      <c r="Y70" s="6"/>
-      <c r="Z70" s="6"/>
-      <c r="AA70" s="8"/>
-      <c r="AB70" s="8"/>
-      <c r="AC70" s="8"/>
-      <c r="AD70" s="8"/>
-      <c r="AE70" s="6"/>
+      <c r="O70" s="5">
+        <v>2742.77</v>
+      </c>
+      <c r="P70" s="5">
+        <v>2742.77</v>
+      </c>
+      <c r="Q70" s="6">
+        <v>-0.2764170804159829</v>
+      </c>
+      <c r="R70" s="7">
+        <v>32</v>
+      </c>
+      <c r="S70" s="6">
+        <v>-0.28888888888888886</v>
+      </c>
+      <c r="T70" s="6">
+        <v>0.38883460880788401</v>
+      </c>
+      <c r="U70" s="6">
+        <v>0.021279181265654794</v>
+      </c>
+      <c r="V70" s="6">
+        <v>0.033602161318666897</v>
+      </c>
+      <c r="W70" s="6">
+        <v>0.010716538390021766</v>
+      </c>
+      <c r="X70" s="8">
+        <v>23.149121052631578</v>
+      </c>
+      <c r="Y70" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z70" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="8">
+        <v>3.6838899999999999</v>
+      </c>
+      <c r="AB70" s="8">
+        <v>4.8768500000000001</v>
+      </c>
+      <c r="AC70" s="8">
+        <v>8.4943939999999998</v>
+      </c>
+      <c r="AD70" s="8">
+        <v>15.059647368421054</v>
+      </c>
+      <c r="AE70" s="6">
+        <v>0.89473684210526316</v>
+      </c>
       <c r="AF70" s="9"/>
-      <c r="AG70" s="5"/>
+      <c r="AG70" s="5">
+        <v>28</v>
+      </c>
       <c r="AH70" s="10">
         <v>2</v>
       </c>
@@ -10492,7 +10846,7 @@
         <v>19657</v>
       </c>
       <c r="B75" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C75" s="4">
         <v>44</v>
@@ -10528,25 +10882,61 @@
       <c t="s" r="N75" s="4">
         <v>52</v>
       </c>
-      <c r="O75" s="5"/>
-      <c r="P75" s="5"/>
-      <c r="Q75" s="6"/>
-      <c r="R75" s="7"/>
-      <c r="S75" s="6"/>
-      <c r="T75" s="6"/>
-      <c r="U75" s="6"/>
-      <c r="V75" s="6"/>
-      <c r="W75" s="6"/>
-      <c r="X75" s="8"/>
-      <c r="Y75" s="6"/>
-      <c r="Z75" s="6"/>
-      <c r="AA75" s="8"/>
-      <c r="AB75" s="8"/>
-      <c r="AC75" s="8"/>
-      <c r="AD75" s="8"/>
-      <c r="AE75" s="6"/>
+      <c r="O75" s="5">
+        <v>3556.1500000000001</v>
+      </c>
+      <c r="P75" s="5">
+        <v>3556.1500000000001</v>
+      </c>
+      <c r="Q75" s="6">
+        <v>-0.17453563785091208</v>
+      </c>
+      <c r="R75" s="7">
+        <v>34</v>
+      </c>
+      <c r="S75" s="6">
+        <v>-0.10526315789473684</v>
+      </c>
+      <c r="T75" s="6">
+        <v>0</v>
+      </c>
+      <c r="U75" s="6">
+        <v>-0.32203647202733293</v>
+      </c>
+      <c r="V75" s="6">
+        <v>0.056108853676026034</v>
+      </c>
+      <c r="W75" s="6">
+        <v>0.025218705622653711</v>
+      </c>
+      <c r="X75" s="8">
+        <v>22.751752631578949</v>
+      </c>
+      <c r="Y75" s="6">
+        <v>0.89473684210526316</v>
+      </c>
+      <c r="Z75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="8">
+        <v>4.4732333333333338</v>
+      </c>
+      <c r="AB75" s="8">
+        <v>6.9101833333333333</v>
+      </c>
+      <c r="AC75" s="8">
+        <v>11.881237</v>
+      </c>
+      <c r="AD75" s="8">
+        <v>18.206142105263158</v>
+      </c>
+      <c r="AE75" s="6">
+        <v>0.84210526315789469</v>
+      </c>
       <c r="AF75" s="9"/>
-      <c r="AG75" s="5"/>
+      <c r="AG75" s="5">
+        <v>-582.87</v>
+      </c>
       <c r="AH75" s="10">
         <v>3</v>
       </c>
@@ -10677,7 +11067,7 @@
         <v>-24.43</v>
       </c>
       <c r="AH76" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI76" s="11"/>
       <c r="AJ76" s="13">
@@ -11980,7 +12370,7 @@
         <v>19689</v>
       </c>
       <c r="B87" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C87" s="4">
         <v>44</v>
@@ -12016,25 +12406,61 @@
       <c t="s" r="N87" s="4">
         <v>52</v>
       </c>
-      <c r="O87" s="5"/>
-      <c r="P87" s="5"/>
-      <c r="Q87" s="6"/>
-      <c r="R87" s="7"/>
-      <c r="S87" s="6"/>
-      <c r="T87" s="6"/>
-      <c r="U87" s="6"/>
-      <c r="V87" s="6"/>
-      <c r="W87" s="6"/>
-      <c r="X87" s="8"/>
-      <c r="Y87" s="6"/>
-      <c r="Z87" s="6"/>
-      <c r="AA87" s="8"/>
-      <c r="AB87" s="8"/>
-      <c r="AC87" s="8"/>
-      <c r="AD87" s="8"/>
-      <c r="AE87" s="6"/>
+      <c r="O87" s="5">
+        <v>2816.71</v>
+      </c>
+      <c r="P87" s="5">
+        <v>2816.71</v>
+      </c>
+      <c r="Q87" s="6">
+        <v>-0.39543124763899862</v>
+      </c>
+      <c r="R87" s="7">
+        <v>27</v>
+      </c>
+      <c r="S87" s="6">
+        <v>-0.48076923076923073</v>
+      </c>
+      <c r="T87" s="6">
+        <v>-0.73620223594193224</v>
+      </c>
+      <c r="U87" s="6">
+        <v>-1.0258912703118177</v>
+      </c>
+      <c r="V87" s="6">
+        <v>0</v>
+      </c>
+      <c r="W87" s="6">
+        <v>-0.038584021784280241</v>
+      </c>
+      <c r="X87" s="8">
+        <v>11.783331578947369</v>
+      </c>
+      <c r="Y87" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z87" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="8">
+        <v>2.5970249999999999</v>
+      </c>
+      <c r="AB87" s="8">
+        <v>4.5374999999999996</v>
+      </c>
+      <c r="AC87" s="8">
+        <v>7.1015350000000002</v>
+      </c>
+      <c r="AD87" s="8">
+        <v>7.4508789473684205</v>
+      </c>
+      <c r="AE87" s="6">
+        <v>1</v>
+      </c>
       <c r="AF87" s="9"/>
-      <c r="AG87" s="5"/>
+      <c r="AG87" s="5">
+        <v>0</v>
+      </c>
       <c r="AH87" s="10">
         <v>5</v>
       </c>
@@ -12297,7 +12723,7 @@
         <v>19694</v>
       </c>
       <c r="B90" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C90" s="4">
         <v>44</v>
@@ -12333,25 +12759,61 @@
       <c t="s" r="N90" s="4">
         <v>52</v>
       </c>
-      <c r="O90" s="5"/>
-      <c r="P90" s="5"/>
-      <c r="Q90" s="6"/>
-      <c r="R90" s="7"/>
-      <c r="S90" s="6"/>
-      <c r="T90" s="6"/>
-      <c r="U90" s="6"/>
-      <c r="V90" s="6"/>
-      <c r="W90" s="6"/>
-      <c r="X90" s="8"/>
-      <c r="Y90" s="6"/>
-      <c r="Z90" s="6"/>
-      <c r="AA90" s="8"/>
-      <c r="AB90" s="8"/>
-      <c r="AC90" s="8"/>
-      <c r="AD90" s="8"/>
-      <c r="AE90" s="6"/>
+      <c r="O90" s="5">
+        <v>2922.5799999999999</v>
+      </c>
+      <c r="P90" s="5">
+        <v>2922.5799999999999</v>
+      </c>
+      <c r="Q90" s="6">
+        <v>-0.068963320229622926</v>
+      </c>
+      <c r="R90" s="7">
+        <v>31</v>
+      </c>
+      <c r="S90" s="6">
+        <v>-0.27906976744186052</v>
+      </c>
+      <c r="T90" s="6">
+        <v>0.74251342991466451</v>
+      </c>
+      <c r="U90" s="6">
+        <v>-2.57930154178842</v>
+      </c>
+      <c r="V90" s="6">
+        <v>0.049667246063409727</v>
+      </c>
+      <c r="W90" s="6">
+        <v>0.011683683594632141</v>
+      </c>
+      <c r="X90" s="8">
+        <v>31.710319047619048</v>
+      </c>
+      <c r="Y90" s="6">
+        <v>0.90476190476190477</v>
+      </c>
+      <c r="Z90" s="6">
+        <v>0.19047619047619047</v>
+      </c>
+      <c r="AA90" s="8">
+        <v>6.3706896551724137</v>
+      </c>
+      <c r="AB90" s="8">
+        <v>11.497619047619047</v>
+      </c>
+      <c r="AC90" s="8">
+        <v>18.188095000000001</v>
+      </c>
+      <c r="AD90" s="8">
+        <v>25.130157142857144</v>
+      </c>
+      <c r="AE90" s="6">
+        <v>0.5714285714285714</v>
+      </c>
       <c r="AF90" s="9"/>
-      <c r="AG90" s="5"/>
+      <c r="AG90" s="5">
+        <v>-138.53</v>
+      </c>
       <c r="AH90" s="10">
         <v>2</v>
       </c>
@@ -12392,7 +12854,7 @@
         <v>19698</v>
       </c>
       <c r="B91" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C91" s="4">
         <v>44</v>
@@ -12428,25 +12890,53 @@
       <c t="s" r="N91" s="4">
         <v>52</v>
       </c>
-      <c r="O91" s="5"/>
-      <c r="P91" s="5"/>
-      <c r="Q91" s="6"/>
-      <c r="R91" s="7"/>
-      <c r="S91" s="6"/>
+      <c r="O91" s="5">
+        <v>0</v>
+      </c>
+      <c r="P91" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R91" s="7">
+        <v>50</v>
+      </c>
+      <c r="S91" s="6">
+        <v>0.063829787234042534</v>
+      </c>
       <c r="T91" s="6"/>
       <c r="U91" s="6"/>
       <c r="V91" s="6"/>
       <c r="W91" s="6"/>
-      <c r="X91" s="8"/>
-      <c r="Y91" s="6"/>
-      <c r="Z91" s="6"/>
-      <c r="AA91" s="8"/>
-      <c r="AB91" s="8"/>
-      <c r="AC91" s="8"/>
-      <c r="AD91" s="8"/>
-      <c r="AE91" s="6"/>
+      <c r="X91" s="8">
+        <v>31.038726470588237</v>
+      </c>
+      <c r="Y91" s="6">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="Z91" s="6">
+        <v>0.088235294117647065</v>
+      </c>
+      <c r="AA91" s="8">
+        <v>7.2443340000000003</v>
+      </c>
+      <c r="AB91" s="8">
+        <v>5.7681818181818176</v>
+      </c>
+      <c r="AC91" s="8">
+        <v>14.241792</v>
+      </c>
+      <c r="AD91" s="8">
+        <v>20.854902941176469</v>
+      </c>
+      <c r="AE91" s="6">
+        <v>0.55882352941176472</v>
+      </c>
       <c r="AF91" s="9"/>
-      <c r="AG91" s="5"/>
+      <c r="AG91" s="5">
+        <v>0</v>
+      </c>
       <c r="AH91" s="10">
         <v>2</v>
       </c>
@@ -13100,7 +13590,7 @@
         <v>19710</v>
       </c>
       <c r="B97" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C97" s="4">
         <v>44</v>
@@ -13136,25 +13626,61 @@
       <c t="s" r="N97" s="4">
         <v>52</v>
       </c>
-      <c r="O97" s="5"/>
-      <c r="P97" s="5"/>
-      <c r="Q97" s="6"/>
-      <c r="R97" s="7"/>
-      <c r="S97" s="6"/>
-      <c r="T97" s="6"/>
-      <c r="U97" s="6"/>
-      <c r="V97" s="6"/>
-      <c r="W97" s="6"/>
-      <c r="X97" s="8"/>
-      <c r="Y97" s="6"/>
-      <c r="Z97" s="6"/>
-      <c r="AA97" s="8"/>
-      <c r="AB97" s="8"/>
-      <c r="AC97" s="8"/>
-      <c r="AD97" s="8"/>
-      <c r="AE97" s="6"/>
+      <c r="O97" s="5">
+        <v>2195.3000000000002</v>
+      </c>
+      <c r="P97" s="5">
+        <v>2195.3000000000002</v>
+      </c>
+      <c r="Q97" s="6">
+        <v>-0.38399676747722922</v>
+      </c>
+      <c r="R97" s="7">
+        <v>37</v>
+      </c>
+      <c r="S97" s="6">
+        <v>-0.27450980392156865</v>
+      </c>
+      <c r="T97" s="6">
+        <v>0.24897590306564024</v>
+      </c>
+      <c r="U97" s="6">
+        <v>-0.088353846854644008</v>
+      </c>
+      <c r="V97" s="6">
+        <v>0.10469115838381997</v>
+      </c>
+      <c r="W97" s="6">
+        <v>0.017846535780986651</v>
+      </c>
+      <c r="X97" s="8">
+        <v>23.540478571428572</v>
+      </c>
+      <c r="Y97" s="6">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="Z97" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="8">
+        <v>4.4970249999999998</v>
+      </c>
+      <c r="AB97" s="8">
+        <v>3.2388916666666669</v>
+      </c>
+      <c r="AC97" s="8">
+        <v>9.353173</v>
+      </c>
+      <c r="AD97" s="8">
+        <v>14.302378571428573</v>
+      </c>
+      <c r="AE97" s="6">
+        <v>0.9285714285714286</v>
+      </c>
       <c r="AF97" s="9"/>
-      <c r="AG97" s="5"/>
+      <c r="AG97" s="5">
+        <v>0</v>
+      </c>
       <c r="AH97" s="10">
         <v>1</v>
       </c>
@@ -14255,10 +14781,10 @@
         <v>1.0666666666666669</v>
       </c>
       <c r="T106" s="6">
-        <v>0.41120769406554608</v>
+        <v>0.42643389045176244</v>
       </c>
       <c r="U106" s="6">
-        <v>-0.087295099406633422</v>
+        <v>-0.072068903020417172</v>
       </c>
       <c r="V106" s="6">
         <v>0.02202193801564975</v>
@@ -15971,7 +16497,7 @@
         <v>0</v>
       </c>
       <c r="AH120" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI120" s="11"/>
       <c r="AJ120" s="13">
@@ -16659,7 +17185,7 @@
         <v>19759</v>
       </c>
       <c r="B126" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C126" s="4">
         <v>44</v>
@@ -16695,25 +17221,61 @@
       <c t="s" r="N126" s="4">
         <v>52</v>
       </c>
-      <c r="O126" s="5"/>
-      <c r="P126" s="5"/>
-      <c r="Q126" s="6"/>
-      <c r="R126" s="7"/>
-      <c r="S126" s="6"/>
-      <c r="T126" s="6"/>
-      <c r="U126" s="6"/>
-      <c r="V126" s="6"/>
-      <c r="W126" s="6"/>
-      <c r="X126" s="8"/>
-      <c r="Y126" s="6"/>
-      <c r="Z126" s="6"/>
-      <c r="AA126" s="8"/>
-      <c r="AB126" s="8"/>
-      <c r="AC126" s="8"/>
-      <c r="AD126" s="8"/>
-      <c r="AE126" s="6"/>
+      <c r="O126" s="5">
+        <v>1647.53</v>
+      </c>
+      <c r="P126" s="5">
+        <v>1647.53</v>
+      </c>
+      <c r="Q126" s="6">
+        <v>-0.56746163014770357</v>
+      </c>
+      <c r="R126" s="7">
+        <v>22</v>
+      </c>
+      <c r="S126" s="6">
+        <v>-0.67164179104477606</v>
+      </c>
+      <c r="T126" s="6">
+        <v>-0.00035082820950149614</v>
+      </c>
+      <c r="U126" s="6">
+        <v>-0.24190636892803166</v>
+      </c>
+      <c r="V126" s="6">
+        <v>0.27058414717789664</v>
+      </c>
+      <c r="W126" s="6">
+        <v>0.24518248529617062</v>
+      </c>
+      <c r="X126" s="8">
+        <v>78.172918749999994</v>
+      </c>
+      <c r="Y126" s="6">
+        <v>0.125</v>
+      </c>
+      <c r="Z126" s="6">
+        <v>0.875</v>
+      </c>
+      <c r="AA126" s="8">
+        <v>4.5856045454545455</v>
+      </c>
+      <c r="AB126" s="8">
+        <v>36.616668750000002</v>
+      </c>
+      <c r="AC126" s="8">
+        <v>41.653123999999998</v>
+      </c>
+      <c r="AD126" s="8">
+        <v>48.557293749999999</v>
+      </c>
+      <c r="AE126" s="6">
+        <v>0</v>
+      </c>
       <c r="AF126" s="9"/>
-      <c r="AG126" s="5"/>
+      <c r="AG126" s="5">
+        <v>0</v>
+      </c>
       <c r="AH126" s="10">
         <v>2</v>
       </c>
@@ -17485,7 +18047,9 @@
       <c r="AB132" s="8">
         <v>6.8576923076923073</v>
       </c>
-      <c r="AC132" s="8"/>
+      <c r="AC132" s="8">
+        <v>10.228573000000001</v>
+      </c>
       <c r="AD132" s="8">
         <v>15.248610714285714</v>
       </c>
@@ -18542,7 +19106,7 @@
         <v>19793</v>
       </c>
       <c r="B141" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C141" s="4">
         <v>44</v>
@@ -18578,25 +19142,61 @@
       <c t="s" r="N141" s="4">
         <v>52</v>
       </c>
-      <c r="O141" s="5"/>
-      <c r="P141" s="5"/>
-      <c r="Q141" s="6"/>
-      <c r="R141" s="7"/>
-      <c r="S141" s="6"/>
-      <c r="T141" s="6"/>
-      <c r="U141" s="6"/>
-      <c r="V141" s="6"/>
-      <c r="W141" s="6"/>
-      <c r="X141" s="8"/>
-      <c r="Y141" s="6"/>
-      <c r="Z141" s="6"/>
-      <c r="AA141" s="8"/>
-      <c r="AB141" s="8"/>
-      <c r="AC141" s="8"/>
-      <c r="AD141" s="8"/>
-      <c r="AE141" s="6"/>
+      <c r="O141" s="5">
+        <v>2152.7800000000002</v>
+      </c>
+      <c r="P141" s="5">
+        <v>2152.7800000000002</v>
+      </c>
+      <c r="Q141" s="6">
+        <v>-0.18789986721390628</v>
+      </c>
+      <c r="R141" s="7">
+        <v>23</v>
+      </c>
+      <c r="S141" s="6">
+        <v>-0.11538461538461542</v>
+      </c>
+      <c r="T141" s="6">
+        <v>0.54438474902219447</v>
+      </c>
+      <c r="U141" s="6">
+        <v>0.22415695054766394</v>
+      </c>
+      <c r="V141" s="6">
+        <v>0.13193684445228959</v>
+      </c>
+      <c r="W141" s="6">
+        <v>0.044988805172846272</v>
+      </c>
+      <c r="X141" s="8">
+        <v>24.130769230769229</v>
+      </c>
+      <c r="Y141" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z141" s="6">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="AA141" s="8">
+        <v>3.9130434782608696</v>
+      </c>
+      <c r="AB141" s="8">
+        <v>5.8782076923076927</v>
+      </c>
+      <c r="AC141" s="8">
+        <v>10.112819999999999</v>
+      </c>
+      <c r="AD141" s="8">
+        <v>18.065384615384616</v>
+      </c>
+      <c r="AE141" s="6">
+        <v>0.69230769230769229</v>
+      </c>
       <c r="AF141" s="9"/>
-      <c r="AG141" s="5"/>
+      <c r="AG141" s="5">
+        <v>0</v>
+      </c>
       <c r="AH141" s="10">
         <v>4</v>
       </c>
@@ -20756,7 +21356,7 @@
         <v>19863</v>
       </c>
       <c r="B159" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C159" s="4">
         <v>44</v>
@@ -20792,25 +21392,61 @@
       <c t="s" r="N159" s="4">
         <v>52</v>
       </c>
-      <c r="O159" s="5"/>
-      <c r="P159" s="5"/>
-      <c r="Q159" s="6"/>
-      <c r="R159" s="7"/>
-      <c r="S159" s="6"/>
-      <c r="T159" s="6"/>
-      <c r="U159" s="6"/>
-      <c r="V159" s="6"/>
-      <c r="W159" s="6"/>
-      <c r="X159" s="8"/>
-      <c r="Y159" s="6"/>
-      <c r="Z159" s="6"/>
-      <c r="AA159" s="8"/>
-      <c r="AB159" s="8"/>
-      <c r="AC159" s="8"/>
-      <c r="AD159" s="8"/>
-      <c r="AE159" s="6"/>
+      <c r="O159" s="5">
+        <v>4366.5500000000002</v>
+      </c>
+      <c r="P159" s="5">
+        <v>4366.5500000000002</v>
+      </c>
+      <c r="Q159" s="6">
+        <v>-0.36990256798019039</v>
+      </c>
+      <c r="R159" s="7">
+        <v>49</v>
+      </c>
+      <c r="S159" s="6">
+        <v>-0.33783783783783783</v>
+      </c>
+      <c r="T159" s="6">
+        <v>0.27268903367647224</v>
+      </c>
+      <c r="U159" s="6">
+        <v>-0.0038565228841991963</v>
+      </c>
+      <c r="V159" s="6">
+        <v>0.06608512441172093</v>
+      </c>
+      <c r="W159" s="6">
+        <v>0.015917371838178884</v>
+      </c>
+      <c r="X159" s="8">
+        <v>31.58235294117647</v>
+      </c>
+      <c r="Y159" s="6">
+        <v>0.58823529411764708</v>
+      </c>
+      <c r="Z159" s="6">
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="AA159" s="8">
+        <v>4.1072916666666668</v>
+      </c>
+      <c r="AB159" s="8">
+        <v>6.4357852941176468</v>
+      </c>
+      <c r="AC159" s="8">
+        <v>10.762254</v>
+      </c>
+      <c r="AD159" s="8">
+        <v>17.699020588235296</v>
+      </c>
+      <c r="AE159" s="6">
+        <v>0.41176470588235292</v>
+      </c>
       <c r="AF159" s="9"/>
-      <c r="AG159" s="5"/>
+      <c r="AG159" s="5">
+        <v>-41.799999999999997</v>
+      </c>
       <c r="AH159" s="10">
         <v>2</v>
       </c>
@@ -21050,7 +21686,9 @@
       <c r="AB161" s="8">
         <v>7.4277666666666669</v>
       </c>
-      <c r="AC161" s="8"/>
+      <c r="AC161" s="8">
+        <v>12.540277</v>
+      </c>
       <c r="AD161" s="8">
         <v>15.483325000000001</v>
       </c>
@@ -22043,7 +22681,7 @@
         <v>0.025599486964457487</v>
       </c>
       <c r="W169" s="6">
-        <v>-0.073801149396936577</v>
+        <v>-0.041366450435340249</v>
       </c>
       <c r="X169" s="8">
         <v>30.476470588235294</v>
@@ -22637,7 +23275,7 @@
         <v>19894</v>
       </c>
       <c r="B174" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C174" s="4">
         <v>44</v>
@@ -22673,25 +23311,61 @@
       <c t="s" r="N174" s="4">
         <v>52</v>
       </c>
-      <c r="O174" s="5"/>
-      <c r="P174" s="5"/>
-      <c r="Q174" s="6"/>
-      <c r="R174" s="7"/>
-      <c r="S174" s="6"/>
-      <c r="T174" s="6"/>
-      <c r="U174" s="6"/>
-      <c r="V174" s="6"/>
-      <c r="W174" s="6"/>
-      <c r="X174" s="8"/>
-      <c r="Y174" s="6"/>
-      <c r="Z174" s="6"/>
-      <c r="AA174" s="8"/>
-      <c r="AB174" s="8"/>
-      <c r="AC174" s="8"/>
-      <c r="AD174" s="8"/>
-      <c r="AE174" s="6"/>
+      <c r="O174" s="5">
+        <v>3797.8499999999999</v>
+      </c>
+      <c r="P174" s="5">
+        <v>3797.8499999999999</v>
+      </c>
+      <c r="Q174" s="6">
+        <v>-0.27640566323526894</v>
+      </c>
+      <c r="R174" s="7">
+        <v>44</v>
+      </c>
+      <c r="S174" s="6">
+        <v>-0.3529411764705882</v>
+      </c>
+      <c r="T174" s="6">
+        <v>0.29292302223626526</v>
+      </c>
+      <c r="U174" s="6">
+        <v>-0.04788822623326356</v>
+      </c>
+      <c r="V174" s="6">
+        <v>0.055373434969785543</v>
+      </c>
+      <c r="W174" s="6">
+        <v>0.0014086917598114723</v>
+      </c>
+      <c r="X174" s="8">
+        <v>21.057812500000001</v>
+      </c>
+      <c r="Y174" s="6">
+        <v>0.9375</v>
+      </c>
+      <c r="Z174" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA174" s="8">
+        <v>5.2410560975609757</v>
+      </c>
+      <c r="AB174" s="8">
+        <v>2.8869781250000002</v>
+      </c>
+      <c r="AC174" s="8">
+        <v>8.2739580000000004</v>
+      </c>
+      <c r="AD174" s="8">
+        <v>15.224478124999999</v>
+      </c>
+      <c r="AE174" s="6">
+        <v>0.96875</v>
+      </c>
       <c r="AF174" s="9"/>
-      <c r="AG174" s="5"/>
+      <c r="AG174" s="5">
+        <v>0</v>
+      </c>
       <c r="AH174" s="10">
         <v>5</v>
       </c>
@@ -22732,7 +23406,7 @@
         <v>19897</v>
       </c>
       <c r="B175" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C175" s="4">
         <v>44</v>
@@ -22768,25 +23442,61 @@
       <c t="s" r="N175" s="4">
         <v>52</v>
       </c>
-      <c r="O175" s="5"/>
-      <c r="P175" s="5"/>
-      <c r="Q175" s="6"/>
-      <c r="R175" s="7"/>
-      <c r="S175" s="6"/>
-      <c r="T175" s="6"/>
-      <c r="U175" s="6"/>
-      <c r="V175" s="6"/>
-      <c r="W175" s="6"/>
-      <c r="X175" s="8"/>
-      <c r="Y175" s="6"/>
-      <c r="Z175" s="6"/>
-      <c r="AA175" s="8"/>
-      <c r="AB175" s="8"/>
-      <c r="AC175" s="8"/>
-      <c r="AD175" s="8"/>
-      <c r="AE175" s="6"/>
+      <c r="O175" s="5">
+        <v>3392.8299999999999</v>
+      </c>
+      <c r="P175" s="5">
+        <v>3392.8299999999999</v>
+      </c>
+      <c r="Q175" s="6">
+        <v>0.44899850523168916</v>
+      </c>
+      <c r="R175" s="7">
+        <v>50</v>
+      </c>
+      <c r="S175" s="6">
+        <v>0.38888888888888884</v>
+      </c>
+      <c r="T175" s="6">
+        <v>-0.056316614743444265</v>
+      </c>
+      <c r="U175" s="6">
+        <v>-0.41591612311845866</v>
+      </c>
+      <c r="V175" s="6">
+        <v>0.025642752510441135</v>
+      </c>
+      <c r="W175" s="6">
+        <v>-0.019393397252441179</v>
+      </c>
+      <c r="X175" s="8">
+        <v>31.578281818181818</v>
+      </c>
+      <c r="Y175" s="6">
+        <v>0.54545454545454541</v>
+      </c>
+      <c r="Z175" s="6">
+        <v>0.15151515151515152</v>
+      </c>
+      <c r="AA175" s="8">
+        <v>5.8962955555555556</v>
+      </c>
+      <c r="AB175" s="8">
+        <v>6.0442718749999997</v>
+      </c>
+      <c r="AC175" s="8">
+        <v>11.86665</v>
+      </c>
+      <c r="AD175" s="8">
+        <v>18.642930303030301</v>
+      </c>
+      <c r="AE175" s="6">
+        <v>0.51515151515151514</v>
+      </c>
       <c r="AF175" s="9"/>
-      <c r="AG175" s="5"/>
+      <c r="AG175" s="5">
+        <v>-202.19999999999999</v>
+      </c>
       <c r="AH175" s="10">
         <v>2</v>
       </c>
@@ -23628,7 +24338,7 @@
         <v>0.059911066261495491</v>
       </c>
       <c r="W182" s="6">
-        <v>0.036981541460960346</v>
+        <v>0.036649933821406418</v>
       </c>
       <c r="X182" s="8">
         <v>21.372857142857143</v>
@@ -23698,7 +24408,7 @@
         <v>19912</v>
       </c>
       <c r="B183" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C183" s="4">
         <v>44</v>
@@ -23734,25 +24444,61 @@
       <c t="s" r="N183" s="4">
         <v>52</v>
       </c>
-      <c r="O183" s="5"/>
-      <c r="P183" s="5"/>
-      <c r="Q183" s="6"/>
-      <c r="R183" s="7"/>
-      <c r="S183" s="6"/>
-      <c r="T183" s="6"/>
-      <c r="U183" s="6"/>
-      <c r="V183" s="6"/>
-      <c r="W183" s="6"/>
-      <c r="X183" s="8"/>
-      <c r="Y183" s="6"/>
-      <c r="Z183" s="6"/>
-      <c r="AA183" s="8"/>
-      <c r="AB183" s="8"/>
-      <c r="AC183" s="8"/>
-      <c r="AD183" s="8"/>
-      <c r="AE183" s="6"/>
+      <c r="O183" s="5">
+        <v>3073.5</v>
+      </c>
+      <c r="P183" s="5">
+        <v>3073.5</v>
+      </c>
+      <c r="Q183" s="6">
+        <v>0.060259001938719914</v>
+      </c>
+      <c r="R183" s="7">
+        <v>37</v>
+      </c>
+      <c r="S183" s="6">
+        <v>0</v>
+      </c>
+      <c r="T183" s="6">
+        <v>15.439538116154223</v>
+      </c>
+      <c r="U183" s="6">
+        <v>11.129048446396617</v>
+      </c>
+      <c r="V183" s="6">
+        <v>0.055331055799577034</v>
+      </c>
+      <c r="W183" s="6">
+        <v>0.014559947942085569</v>
+      </c>
+      <c r="X183" s="8">
+        <v>23.949999999999999</v>
+      </c>
+      <c r="Y183" s="6">
+        <v>0.65517241379310343</v>
+      </c>
+      <c r="Z183" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA183" s="8">
+        <v>5.7247756756756756</v>
+      </c>
+      <c r="AB183" s="8">
+        <v>3.2602576923076922</v>
+      </c>
+      <c r="AC183" s="8">
+        <v>9.1970369999999999</v>
+      </c>
+      <c r="AD183" s="8">
+        <v>16.493679310344827</v>
+      </c>
+      <c r="AE183" s="6">
+        <v>0.86206896551724133</v>
+      </c>
       <c r="AF183" s="9"/>
-      <c r="AG183" s="5"/>
+      <c r="AG183" s="5">
+        <v>-74.400000000000006</v>
+      </c>
       <c r="AH183" s="10">
         <v>4</v>
       </c>
@@ -24112,7 +24858,7 @@
         <v>19927</v>
       </c>
       <c r="B187" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C187" s="4">
         <v>44</v>
@@ -24148,25 +24894,61 @@
       <c t="s" r="N187" s="4">
         <v>52</v>
       </c>
-      <c r="O187" s="5"/>
-      <c r="P187" s="5"/>
-      <c r="Q187" s="6"/>
-      <c r="R187" s="7"/>
-      <c r="S187" s="6"/>
-      <c r="T187" s="6"/>
-      <c r="U187" s="6"/>
-      <c r="V187" s="6"/>
-      <c r="W187" s="6"/>
-      <c r="X187" s="8"/>
-      <c r="Y187" s="6"/>
-      <c r="Z187" s="6"/>
-      <c r="AA187" s="8"/>
-      <c r="AB187" s="8"/>
-      <c r="AC187" s="8"/>
-      <c r="AD187" s="8"/>
-      <c r="AE187" s="6"/>
+      <c r="O187" s="5">
+        <v>505.24000000000001</v>
+      </c>
+      <c r="P187" s="5">
+        <v>505.24000000000001</v>
+      </c>
+      <c r="Q187" s="6">
+        <v>-0.69310202395704246</v>
+      </c>
+      <c r="R187" s="7">
+        <v>6</v>
+      </c>
+      <c r="S187" s="6">
+        <v>-0.68421052631578949</v>
+      </c>
+      <c r="T187" s="6">
+        <v>0</v>
+      </c>
+      <c r="U187" s="6">
+        <v>-0.2877246457129285</v>
+      </c>
+      <c r="V187" s="6">
+        <v>0.21941255640883539</v>
+      </c>
+      <c r="W187" s="6">
+        <v>0.044129522603119309</v>
+      </c>
+      <c r="X187" s="8">
+        <v>31.286660000000001</v>
+      </c>
+      <c r="Y187" s="6">
+        <v>0.59999999999999998</v>
+      </c>
+      <c r="Z187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA187" s="8">
+        <v>7.9972166666666666</v>
+      </c>
+      <c r="AB187" s="8">
+        <v>7.4833400000000001</v>
+      </c>
+      <c r="AC187" s="8">
+        <v>15.566666</v>
+      </c>
+      <c r="AD187" s="8">
+        <v>22.50666</v>
+      </c>
+      <c r="AE187" s="6">
+        <v>0.59999999999999998</v>
+      </c>
       <c r="AF187" s="9"/>
-      <c r="AG187" s="5"/>
+      <c r="AG187" s="5">
+        <v>0</v>
+      </c>
       <c r="AH187" s="10">
         <v>1</v>
       </c>
@@ -24340,7 +25122,7 @@
         <v>19930</v>
       </c>
       <c r="B189" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C189" s="4">
         <v>44</v>
@@ -24376,25 +25158,61 @@
       <c t="s" r="N189" s="4">
         <v>52</v>
       </c>
-      <c r="O189" s="5"/>
-      <c r="P189" s="5"/>
-      <c r="Q189" s="6"/>
-      <c r="R189" s="7"/>
-      <c r="S189" s="6"/>
-      <c r="T189" s="6"/>
-      <c r="U189" s="6"/>
-      <c r="V189" s="6"/>
-      <c r="W189" s="6"/>
-      <c r="X189" s="8"/>
-      <c r="Y189" s="6"/>
-      <c r="Z189" s="6"/>
-      <c r="AA189" s="8"/>
-      <c r="AB189" s="8"/>
-      <c r="AC189" s="8"/>
-      <c r="AD189" s="8"/>
-      <c r="AE189" s="6"/>
+      <c r="O189" s="5">
+        <v>4052.0300000000002</v>
+      </c>
+      <c r="P189" s="5">
+        <v>4052.0300000000002</v>
+      </c>
+      <c r="Q189" s="6">
+        <v>0.4862853411975292</v>
+      </c>
+      <c r="R189" s="7">
+        <v>55</v>
+      </c>
+      <c r="S189" s="6">
+        <v>0.17021276595744683</v>
+      </c>
+      <c r="T189" s="6">
+        <v>0.34824149870558707</v>
+      </c>
+      <c r="U189" s="6">
+        <v>0.041375557436642868</v>
+      </c>
+      <c r="V189" s="6">
+        <v>0.084702359064468921</v>
+      </c>
+      <c r="W189" s="6">
+        <v>0.048609339022662713</v>
+      </c>
+      <c r="X189" s="8">
+        <v>28.056209803921568</v>
+      </c>
+      <c r="Y189" s="6">
+        <v>0.15686274509803921</v>
+      </c>
+      <c r="Z189" s="6">
+        <v>0.078431372549019607</v>
+      </c>
+      <c r="AA189" s="8">
+        <v>4.7307465517241383</v>
+      </c>
+      <c r="AB189" s="8">
+        <v>11.397711764705884</v>
+      </c>
+      <c r="AC189" s="8">
+        <v>16.130082999999999</v>
+      </c>
+      <c r="AD189" s="8">
+        <v>23.023201960784313</v>
+      </c>
+      <c r="AE189" s="6">
+        <v>0.62745098039215685</v>
+      </c>
       <c r="AF189" s="9"/>
-      <c r="AG189" s="5"/>
+      <c r="AG189" s="5">
+        <v>0</v>
+      </c>
       <c r="AH189" s="10">
         <v>3</v>
       </c>
@@ -24435,7 +25253,7 @@
         <v>19931</v>
       </c>
       <c r="B190" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C190" s="4">
         <v>44</v>
@@ -24471,25 +25289,61 @@
       <c t="s" r="N190" s="4">
         <v>52</v>
       </c>
-      <c r="O190" s="5"/>
-      <c r="P190" s="5"/>
-      <c r="Q190" s="6"/>
-      <c r="R190" s="7"/>
-      <c r="S190" s="6"/>
-      <c r="T190" s="6"/>
-      <c r="U190" s="6"/>
-      <c r="V190" s="6"/>
-      <c r="W190" s="6"/>
-      <c r="X190" s="8"/>
-      <c r="Y190" s="6"/>
-      <c r="Z190" s="6"/>
-      <c r="AA190" s="8"/>
-      <c r="AB190" s="8"/>
-      <c r="AC190" s="8"/>
-      <c r="AD190" s="8"/>
-      <c r="AE190" s="6"/>
+      <c r="O190" s="5">
+        <v>3901.9099999999999</v>
+      </c>
+      <c r="P190" s="5">
+        <v>3901.9099999999999</v>
+      </c>
+      <c r="Q190" s="6">
+        <v>0.36347466925716532</v>
+      </c>
+      <c r="R190" s="7">
+        <v>37</v>
+      </c>
+      <c r="S190" s="6">
+        <v>-0.11904761904761907</v>
+      </c>
+      <c r="T190" s="6">
+        <v>3.2446053086821585</v>
+      </c>
+      <c r="U190" s="6">
+        <v>2.960608496864356</v>
+      </c>
+      <c r="V190" s="6">
+        <v>0.081764187282638498</v>
+      </c>
+      <c r="W190" s="6">
+        <v>0.042309151159304038</v>
+      </c>
+      <c r="X190" s="8">
+        <v>27.011999999999997</v>
+      </c>
+      <c r="Y190" s="6">
+        <v>0.59999999999999998</v>
+      </c>
+      <c r="Z190" s="6">
+        <v>0.080000000000000002</v>
+      </c>
+      <c r="AA190" s="8">
+        <v>5.1476861111111107</v>
+      </c>
+      <c r="AB190" s="8">
+        <v>7.8760000000000003</v>
+      </c>
+      <c r="AC190" s="8">
+        <v>13.179333</v>
+      </c>
+      <c r="AD190" s="8">
+        <v>20.105999999999998</v>
+      </c>
+      <c r="AE190" s="6">
+        <v>0.59999999999999998</v>
+      </c>
       <c r="AF190" s="9"/>
-      <c r="AG190" s="5"/>
+      <c r="AG190" s="5">
+        <v>-211.80000000000001</v>
+      </c>
       <c r="AH190" s="10">
         <v>2</v>
       </c>
@@ -25707,7 +26561,7 @@
         <v>19954</v>
       </c>
       <c r="B200" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C200" s="4">
         <v>44</v>
@@ -25743,25 +26597,61 @@
       <c t="s" r="N200" s="4">
         <v>52</v>
       </c>
-      <c r="O200" s="5"/>
-      <c r="P200" s="5"/>
-      <c r="Q200" s="6"/>
-      <c r="R200" s="7"/>
-      <c r="S200" s="6"/>
-      <c r="T200" s="6"/>
-      <c r="U200" s="6"/>
-      <c r="V200" s="6"/>
-      <c r="W200" s="6"/>
-      <c r="X200" s="8"/>
-      <c r="Y200" s="6"/>
-      <c r="Z200" s="6"/>
-      <c r="AA200" s="8"/>
-      <c r="AB200" s="8"/>
-      <c r="AC200" s="8"/>
-      <c r="AD200" s="8"/>
-      <c r="AE200" s="6"/>
+      <c r="O200" s="5">
+        <v>731.97000000000003</v>
+      </c>
+      <c r="P200" s="5">
+        <v>731.97000000000003</v>
+      </c>
+      <c r="Q200" s="6">
+        <v>-0.42706523270558394</v>
+      </c>
+      <c r="R200" s="7">
+        <v>10</v>
+      </c>
+      <c r="S200" s="6">
+        <v>-0.44444444444444442</v>
+      </c>
+      <c r="T200" s="6">
+        <v>0</v>
+      </c>
+      <c r="U200" s="6">
+        <v>-0.34904435974151948</v>
+      </c>
+      <c r="V200" s="6">
+        <v>0.37347637198245826</v>
+      </c>
+      <c r="W200" s="6">
+        <v>0.23452258972362255</v>
+      </c>
+      <c r="X200" s="8">
+        <v>28.838899999999999</v>
+      </c>
+      <c r="Y200" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA200" s="8">
+        <v>5.3733300000000002</v>
+      </c>
+      <c r="AB200" s="8">
+        <v>8.3166666666666664</v>
+      </c>
+      <c r="AC200" s="8">
+        <v>15.516666000000001</v>
+      </c>
+      <c r="AD200" s="8">
+        <v>22.483333333333334</v>
+      </c>
+      <c r="AE200" s="6">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="AF200" s="9"/>
-      <c r="AG200" s="5"/>
+      <c r="AG200" s="5">
+        <v>-91.799999999999997</v>
+      </c>
       <c r="AH200" s="10">
         <v>3</v>
       </c>
@@ -26504,7 +27394,7 @@
         <v>19962</v>
       </c>
       <c r="B207" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C207" s="4">
         <v>44</v>
@@ -26540,25 +27430,57 @@
       <c t="s" r="N207" s="4">
         <v>52</v>
       </c>
-      <c r="O207" s="5"/>
-      <c r="P207" s="5"/>
+      <c r="O207" s="5">
+        <v>1998.04</v>
+      </c>
+      <c r="P207" s="5">
+        <v>1998.04</v>
+      </c>
       <c r="Q207" s="6"/>
-      <c r="R207" s="7"/>
+      <c r="R207" s="7">
+        <v>23</v>
+      </c>
       <c r="S207" s="6"/>
-      <c r="T207" s="6"/>
-      <c r="U207" s="6"/>
-      <c r="V207" s="6"/>
-      <c r="W207" s="6"/>
-      <c r="X207" s="8"/>
-      <c r="Y207" s="6"/>
-      <c r="Z207" s="6"/>
-      <c r="AA207" s="8"/>
-      <c r="AB207" s="8"/>
-      <c r="AC207" s="8"/>
-      <c r="AD207" s="8"/>
-      <c r="AE207" s="6"/>
+      <c r="T207" s="6">
+        <v>-0.0025825308802626575</v>
+      </c>
+      <c r="U207" s="6">
+        <v>-0.38540769954555465</v>
+      </c>
+      <c r="V207" s="6">
+        <v>0.2466064242958099</v>
+      </c>
+      <c r="W207" s="6">
+        <v>0.14898575604092013</v>
+      </c>
+      <c r="X207" s="8">
+        <v>29.662500000000001</v>
+      </c>
+      <c r="Y207" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z207" s="6">
+        <v>0.125</v>
+      </c>
+      <c r="AA207" s="8">
+        <v>6.1246391304347831</v>
+      </c>
+      <c r="AB207" s="8">
+        <v>9.875</v>
+      </c>
+      <c r="AC207" s="8">
+        <v>16.177083</v>
+      </c>
+      <c r="AD207" s="8">
+        <v>23.139587500000001</v>
+      </c>
+      <c r="AE207" s="6">
+        <v>0.75</v>
+      </c>
       <c r="AF207" s="9"/>
-      <c r="AG207" s="5"/>
+      <c r="AG207" s="5">
+        <v>-66.900000000000006</v>
+      </c>
       <c r="AH207" s="10">
         <v>4</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-14).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-14).xlsx
@@ -915,33 +915,33 @@
   </si>
   <si>
     <t>215
-168</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>R$ 737.898,31</t>
-  </si>
-  <si>
-    <t>R$ 4.054,39
-R$ 4.196,22</t>
-  </si>
-  <si>
-    <t>(11.4%)
-(8.6%)</t>
-  </si>
-  <si>
-    <t>44.7</t>
-  </si>
-  <si>
-    <t>(15.9%)</t>
-  </si>
-  <si>
-    <t>69.8%</t>
-  </si>
-  <si>
-    <t>28.0%</t>
+170</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 744.922,64</t>
+  </si>
+  <si>
+    <t>R$ 4.048,49
+R$ 4.188,17</t>
+  </si>
+  <si>
+    <t>(11.2%)
+(8.4%)</t>
+  </si>
+  <si>
+    <t>44.6</t>
+  </si>
+  <si>
+    <t>(15.7%)</t>
+  </si>
+  <si>
+    <t>69.1%</t>
+  </si>
+  <si>
+    <t>27.5%</t>
   </si>
   <si>
     <t>3.9%</t>
@@ -950,16 +950,16 @@
     <t>0.2%</t>
   </si>
   <si>
-    <t>26.2</t>
+    <t>26.1</t>
   </si>
   <si>
     <t>72.8%</t>
   </si>
   <si>
-    <t>8.2%</t>
-  </si>
-  <si>
-    <t>4.5</t>
+    <t>8.1%</t>
+  </si>
+  <si>
+    <t>4.6</t>
   </si>
   <si>
     <t>6.9</t>
@@ -971,7 +971,7 @@
     <t>18.0</t>
   </si>
   <si>
-    <t>74.4%</t>
+    <t>74.6%</t>
   </si>
   <si>
     <t>-R$ 15.136,65</t>
@@ -2216,10 +2216,10 @@
         <v>-0.34177215189873422</v>
       </c>
       <c r="T7" s="6">
-        <v>0.35489005510619975</v>
+        <v>0.35168589466107009</v>
       </c>
       <c r="U7" s="6">
-        <v>0.017964037489725346</v>
+        <v>0.014759877044595651</v>
       </c>
       <c r="V7" s="6">
         <v>0.058989654820211762</v>
@@ -3028,7 +3028,9 @@
       <c r="AB13" s="8">
         <v>8.3329938775510204</v>
       </c>
-      <c r="AC13" s="8"/>
+      <c r="AC13" s="8">
+        <v>21.256122000000001</v>
+      </c>
       <c r="AD13" s="8">
         <v>28.203402040816325</v>
       </c>
@@ -11158,10 +11160,10 @@
         <v>-0.23529411764705888</v>
       </c>
       <c r="T77" s="6">
-        <v>0.3250460478543471</v>
+        <v>0.33886040415847546</v>
       </c>
       <c r="U77" s="6">
-        <v>0.0079047340736411471</v>
+        <v>0.02171909037776951</v>
       </c>
       <c r="V77" s="6">
         <v>0.03668907071887785</v>
@@ -14243,7 +14245,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>44</v>
@@ -14279,25 +14281,59 @@
       <c t="s" r="N102" s="4">
         <v>52</v>
       </c>
-      <c r="O102" s="5"/>
-      <c r="P102" s="5"/>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="7"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
-      <c r="X102" s="8"/>
-      <c r="Y102" s="6"/>
-      <c r="Z102" s="6"/>
-      <c r="AA102" s="8"/>
-      <c r="AB102" s="8"/>
+      <c r="O102" s="5">
+        <v>3131.4899999999998</v>
+      </c>
+      <c r="P102" s="5">
+        <v>3131.4899999999998</v>
+      </c>
+      <c r="Q102" s="6">
+        <v>0.14435385734175776</v>
+      </c>
+      <c r="R102" s="7">
+        <v>36</v>
+      </c>
+      <c r="S102" s="6">
+        <v>0.058823529411764719</v>
+      </c>
+      <c r="T102" s="6">
+        <v>-0.0016919421744920151</v>
+      </c>
+      <c r="U102" s="6">
+        <v>-0.33565436900644746</v>
+      </c>
+      <c r="V102" s="6">
+        <v>0.01525008861596237</v>
+      </c>
+      <c r="W102" s="6">
+        <v>-0.012618434036193633</v>
+      </c>
+      <c r="X102" s="8">
+        <v>20.268453571428573</v>
+      </c>
+      <c r="Y102" s="6">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="Z102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="8">
+        <v>8.5991</v>
+      </c>
+      <c r="AB102" s="8">
+        <v>2.0192307692307692</v>
+      </c>
       <c r="AC102" s="8"/>
-      <c r="AD102" s="8"/>
-      <c r="AE102" s="6"/>
+      <c r="AD102" s="8">
+        <v>13.471428571428572</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>0.9285714285714286</v>
+      </c>
       <c r="AF102" s="9"/>
-      <c r="AG102" s="5"/>
+      <c r="AG102" s="5">
+        <v>0</v>
+      </c>
       <c r="AH102" s="10">
         <v>2</v>
       </c>
@@ -16328,10 +16364,10 @@
         <v>0.39473684210526305</v>
       </c>
       <c r="T119" s="6">
-        <v>0.33541786331838719</v>
+        <v>0.32514360886705601</v>
       </c>
       <c r="U119" s="6">
-        <v>0.010207902911834753</v>
+        <v>-6.6351539496436161E-05</v>
       </c>
       <c r="V119" s="6">
         <v>0.021900805301300379</v>
@@ -24182,7 +24218,7 @@
         <v>19910</v>
       </c>
       <c r="B181" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C181" s="4">
         <v>44</v>
@@ -24218,25 +24254,61 @@
       <c t="s" r="N181" s="4">
         <v>52</v>
       </c>
-      <c r="O181" s="5"/>
-      <c r="P181" s="5"/>
-      <c r="Q181" s="6"/>
-      <c r="R181" s="7"/>
-      <c r="S181" s="6"/>
-      <c r="T181" s="6"/>
-      <c r="U181" s="6"/>
-      <c r="V181" s="6"/>
-      <c r="W181" s="6"/>
-      <c r="X181" s="8"/>
-      <c r="Y181" s="6"/>
-      <c r="Z181" s="6"/>
-      <c r="AA181" s="8"/>
-      <c r="AB181" s="8"/>
-      <c r="AC181" s="8"/>
-      <c r="AD181" s="8"/>
-      <c r="AE181" s="6"/>
+      <c r="O181" s="5">
+        <v>3892.8400000000001</v>
+      </c>
+      <c r="P181" s="5">
+        <v>3892.8400000000001</v>
+      </c>
+      <c r="Q181" s="6">
+        <v>0.32706986067409605</v>
+      </c>
+      <c r="R181" s="7">
+        <v>35</v>
+      </c>
+      <c r="S181" s="6">
+        <v>0.16666666666666674</v>
+      </c>
+      <c r="T181" s="6">
+        <v>0.087596716022235691</v>
+      </c>
+      <c r="U181" s="6">
+        <v>-0.17321544168267894</v>
+      </c>
+      <c r="V181" s="6">
+        <v>0.081022980651657903</v>
+      </c>
+      <c r="W181" s="6">
+        <v>0.051910558872185854</v>
+      </c>
+      <c r="X181" s="8">
+        <v>15.061804166666667</v>
+      </c>
+      <c r="Y181" s="6">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="Z181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA181" s="8">
+        <v>4.2128571428571426</v>
+      </c>
+      <c r="AB181" s="8">
+        <v>3.5592555555555552</v>
+      </c>
+      <c r="AC181" s="8">
+        <v>7.4925920000000001</v>
+      </c>
+      <c r="AD181" s="8">
+        <v>10.802083333333334</v>
+      </c>
+      <c r="AE181" s="6">
+        <v>1</v>
+      </c>
       <c r="AF181" s="9"/>
-      <c r="AG181" s="5"/>
+      <c r="AG181" s="5">
+        <v>0</v>
+      </c>
       <c r="AH181" s="10">
         <v>3</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-14).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-14).xlsx
@@ -915,39 +915,39 @@
   </si>
   <si>
     <t>215
-170</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R$ 744.922,64</t>
-  </si>
-  <si>
-    <t>R$ 4.048,49
-R$ 4.188,17</t>
-  </si>
-  <si>
-    <t>(11.2%)
-(8.4%)</t>
+171</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 748.326,69</t>
+  </si>
+  <si>
+    <t>R$ 4.045,01
+R$ 4.183,59</t>
+  </si>
+  <si>
+    <t>(11.4%)
+(8.6%)</t>
   </si>
   <si>
     <t>44.6</t>
   </si>
   <si>
-    <t>(15.7%)</t>
-  </si>
-  <si>
-    <t>69.1%</t>
-  </si>
-  <si>
-    <t>27.5%</t>
+    <t>(15.8%)</t>
+  </si>
+  <si>
+    <t>70.6%</t>
+  </si>
+  <si>
+    <t>28.9%</t>
   </si>
   <si>
     <t>3.9%</t>
   </si>
   <si>
-    <t>0.2%</t>
+    <t>0.3%</t>
   </si>
   <si>
     <t>26.1</t>
@@ -956,7 +956,7 @@
     <t>72.8%</t>
   </si>
   <si>
-    <t>8.1%</t>
+    <t>8.2%</t>
   </si>
   <si>
     <t>4.6</t>
@@ -971,7 +971,7 @@
     <t>18.0</t>
   </si>
   <si>
-    <t>74.6%</t>
+    <t>74.5%</t>
   </si>
   <si>
     <t>-R$ 15.136,65</t>
@@ -3928,7 +3928,7 @@
         <v>0.029804864103964091</v>
       </c>
       <c r="W20" s="6">
-        <v>0.0043855786674181444</v>
+        <v>0.0047689950291355792</v>
       </c>
       <c r="X20" s="8">
         <v>20.816666666666666</v>
@@ -4840,7 +4840,7 @@
         <v>-219.5</v>
       </c>
       <c r="AH27" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI27" s="11"/>
       <c r="AJ27" s="13">
@@ -12632,7 +12632,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12666,25 +12666,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>3404.0500000000002</v>
+      </c>
+      <c r="P89" s="5">
+        <v>3404.0500000000002</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.38323488911436432</v>
+      </c>
+      <c r="R89" s="7">
+        <v>38</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.34482758620689657</v>
+      </c>
+      <c r="T89" s="6">
+        <v>3.4372484540473844</v>
+      </c>
+      <c r="U89" s="6">
+        <v>3.0907670568881183</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.04375244194415475</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.0086942024940879249</v>
+      </c>
+      <c r="X89" s="8">
+        <v>35.638888888888886</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>6.7222230769230764</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>12.223529411764707</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>26.812961111111111</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.22222222222222221</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>0</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -14206,7 +14240,7 @@
         <v>0</v>
       </c>
       <c r="AH101" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI101" s="11"/>
       <c r="AJ101" s="13">
@@ -14323,7 +14357,9 @@
       <c r="AB102" s="8">
         <v>2.0192307692307692</v>
       </c>
-      <c r="AC102" s="8"/>
+      <c r="AC102" s="8">
+        <v>10.174977</v>
+      </c>
       <c r="AD102" s="8">
         <v>13.471428571428572</v>
       </c>
@@ -16005,7 +16041,9 @@
       <c r="Z116" s="6"/>
       <c r="AA116" s="8"/>
       <c r="AB116" s="8"/>
-      <c r="AC116" s="8"/>
+      <c r="AC116" s="8">
+        <v>7.1892849999999999</v>
+      </c>
       <c r="AD116" s="8"/>
       <c r="AE116" s="6"/>
       <c r="AF116" s="9"/>
@@ -20111,16 +20149,16 @@
         <v>-0.32203389830508478</v>
       </c>
       <c r="T148" s="6">
-        <v>0</v>
+        <v>0.4096886834210397</v>
       </c>
       <c r="U148" s="6">
-        <v>-0.29792394137608813</v>
+        <v>0.11176474204495154</v>
       </c>
       <c r="V148" s="6">
         <v>0.081743194560566557</v>
       </c>
       <c r="W148" s="6">
-        <v>0.022593659322283972</v>
+        <v>0.043812244872866765</v>
       </c>
       <c r="X148" s="8">
         <v>30.369642857142857</v>
@@ -24706,7 +24744,7 @@
         <v>19923</v>
       </c>
       <c r="B185" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C185" s="4">
         <v>44</v>
@@ -25677,7 +25715,7 @@
         <v>0</v>
       </c>
       <c r="AH192" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI192" s="11"/>
       <c r="AJ192" s="13">
@@ -26988,7 +27026,7 @@
         <v>19957</v>
       </c>
       <c r="B203" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C203" s="4">
         <v>44</v>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-14).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-14).xlsx
@@ -915,36 +915,36 @@
   </si>
   <si>
     <t>215
-171</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>R$ 748.326,69</t>
-  </si>
-  <si>
-    <t>R$ 4.045,01
-R$ 4.183,59</t>
-  </si>
-  <si>
-    <t>(11.4%)
+177</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>R$ 768.569,85</t>
+  </si>
+  <si>
+    <t>R$ 4.023,93
+R$ 4.156,14</t>
+  </si>
+  <si>
+    <t>(11.2%)
 (8.6%)</t>
   </si>
   <si>
-    <t>44.6</t>
-  </si>
-  <si>
-    <t>(15.8%)</t>
-  </si>
-  <si>
-    <t>70.6%</t>
-  </si>
-  <si>
-    <t>28.9%</t>
-  </si>
-  <si>
-    <t>3.9%</t>
+    <t>44.2</t>
+  </si>
+  <si>
+    <t>(15.7%)</t>
+  </si>
+  <si>
+    <t>69.4%</t>
+  </si>
+  <si>
+    <t>28.1%</t>
+  </si>
+  <si>
+    <t>4.0%</t>
   </si>
   <si>
     <t>0.3%</t>
@@ -953,16 +953,16 @@
     <t>26.1</t>
   </si>
   <si>
-    <t>72.8%</t>
-  </si>
-  <si>
-    <t>8.2%</t>
+    <t>73.2%</t>
+  </si>
+  <si>
+    <t>8.1%</t>
   </si>
   <si>
     <t>4.6</t>
   </si>
   <si>
-    <t>6.9</t>
+    <t>6.8</t>
   </si>
   <si>
     <t>11.4</t>
@@ -971,10 +971,10 @@
     <t>18.0</t>
   </si>
   <si>
-    <t>74.5%</t>
-  </si>
-  <si>
-    <t>-R$ 15.136,65</t>
+    <t>74.8%</t>
+  </si>
+  <si>
+    <t>-R$ 15.112,65</t>
   </si>
   <si>
     <t>2.94</t>
@@ -2069,7 +2069,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2105,25 +2105,61 @@
       <c t="s" r="N6" s="4">
         <v>52</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="6"/>
+      <c r="O6" s="5">
+        <v>9467</v>
+      </c>
+      <c r="P6" s="5">
+        <v>9467</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>0.3365352578763392</v>
+      </c>
+      <c r="R6" s="7">
+        <v>96</v>
+      </c>
+      <c r="S6" s="6">
+        <v>0.26315789473684204</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0.30109196155064966</v>
+      </c>
+      <c r="U6" s="6">
+        <v>0.014126713848103939</v>
+      </c>
+      <c r="V6" s="6">
+        <v>0.033612327030738354</v>
+      </c>
+      <c r="W6" s="6">
+        <v>0.0044108904616034644</v>
+      </c>
+      <c r="X6" s="8">
+        <v>22.226666666666667</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>0.97333333333333338</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>5.894148936170212</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>3.0746666666666664</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>9.2486660000000001</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>16.207333333333334</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>0.95999999999999996</v>
+      </c>
       <c r="AF6" s="9"/>
-      <c r="AG6" s="5"/>
+      <c r="AG6" s="5">
+        <v>0</v>
+      </c>
       <c r="AH6" s="10">
         <v>5</v>
       </c>
@@ -7886,7 +7922,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7922,25 +7958,59 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
+      <c r="O51" s="5">
+        <v>1182.0899999999999</v>
+      </c>
+      <c r="P51" s="5">
+        <v>1182.0899999999999</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.035390792029115659</v>
+      </c>
+      <c r="R51" s="7">
+        <v>11</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.15384615384615385</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.32292803424443151</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.024979062507930871</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.083312184351445329</v>
+      </c>
+      <c r="X51" s="8">
+        <v>31.06945</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>6.0333363636363631</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>18.233340000000002</v>
+      </c>
       <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="AD51" s="8">
+        <v>28.800000000000001</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0.33333333333333331</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -8813,7 +8883,9 @@
       <c r="Z58" s="6"/>
       <c r="AA58" s="8"/>
       <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
+      <c r="AC58" s="8">
+        <v>7.6833330000000002</v>
+      </c>
       <c r="AD58" s="8"/>
       <c r="AE58" s="6"/>
       <c r="AF58" s="9"/>
@@ -20490,7 +20562,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>44</v>
@@ -20526,25 +20598,61 @@
       <c t="s" r="N151" s="4">
         <v>52</v>
       </c>
-      <c r="O151" s="5"/>
-      <c r="P151" s="5"/>
-      <c r="Q151" s="6"/>
-      <c r="R151" s="7"/>
-      <c r="S151" s="6"/>
-      <c r="T151" s="6"/>
-      <c r="U151" s="6"/>
-      <c r="V151" s="6"/>
-      <c r="W151" s="6"/>
-      <c r="X151" s="8"/>
-      <c r="Y151" s="6"/>
-      <c r="Z151" s="6"/>
-      <c r="AA151" s="8"/>
-      <c r="AB151" s="8"/>
-      <c r="AC151" s="8"/>
-      <c r="AD151" s="8"/>
-      <c r="AE151" s="6"/>
+      <c r="O151" s="5">
+        <v>2117.3499999999999</v>
+      </c>
+      <c r="P151" s="5">
+        <v>2117.3499999999999</v>
+      </c>
+      <c r="Q151" s="6">
+        <v>-0.38640163908297132</v>
+      </c>
+      <c r="R151" s="7">
+        <v>28</v>
+      </c>
+      <c r="S151" s="6">
+        <v>-0.30000000000000004</v>
+      </c>
+      <c r="T151" s="6">
+        <v>0.22359992443384422</v>
+      </c>
+      <c r="U151" s="6">
+        <v>-0.070158783384891496</v>
+      </c>
+      <c r="V151" s="6">
+        <v>0.076478617139348712</v>
+      </c>
+      <c r="W151" s="6">
+        <v>0.019487567005927221</v>
+      </c>
+      <c r="X151" s="8">
+        <v>22.425395238095238</v>
+      </c>
+      <c r="Y151" s="6">
+        <v>0.80952380952380953</v>
+      </c>
+      <c r="Z151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="8">
+        <v>3.6136892857142859</v>
+      </c>
+      <c r="AB151" s="8">
+        <v>3.0166666666666666</v>
+      </c>
+      <c r="AC151" s="8">
+        <v>6.6722210000000004</v>
+      </c>
+      <c r="AD151" s="8">
+        <v>13.580157142857141</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>0.90476190476190477</v>
+      </c>
       <c r="AF151" s="9"/>
-      <c r="AG151" s="5"/>
+      <c r="AG151" s="5">
+        <v>0</v>
+      </c>
       <c r="AH151" s="10">
         <v>5</v>
       </c>
@@ -21240,7 +21348,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>44</v>
@@ -21276,25 +21384,61 @@
       <c t="s" r="N157" s="4">
         <v>52</v>
       </c>
-      <c r="O157" s="5"/>
-      <c r="P157" s="5"/>
-      <c r="Q157" s="6"/>
-      <c r="R157" s="7"/>
-      <c r="S157" s="6"/>
-      <c r="T157" s="6"/>
-      <c r="U157" s="6"/>
-      <c r="V157" s="6"/>
-      <c r="W157" s="6"/>
-      <c r="X157" s="8"/>
-      <c r="Y157" s="6"/>
-      <c r="Z157" s="6"/>
-      <c r="AA157" s="8"/>
-      <c r="AB157" s="8"/>
-      <c r="AC157" s="8"/>
-      <c r="AD157" s="8"/>
-      <c r="AE157" s="6"/>
+      <c r="O157" s="5">
+        <v>1698.3599999999999</v>
+      </c>
+      <c r="P157" s="5">
+        <v>1698.3599999999999</v>
+      </c>
+      <c r="Q157" s="6">
+        <v>-0.37266924736266671</v>
+      </c>
+      <c r="R157" s="7">
+        <v>19</v>
+      </c>
+      <c r="S157" s="6">
+        <v>-0.3666666666666667</v>
+      </c>
+      <c r="T157" s="6">
+        <v>0.26745189476907139</v>
+      </c>
+      <c r="U157" s="6">
+        <v>-0.034839727737346622</v>
+      </c>
+      <c r="V157" s="6">
+        <v>0.12958648343107468</v>
+      </c>
+      <c r="W157" s="6">
+        <v>0.076971019100779581</v>
+      </c>
+      <c r="X157" s="8">
+        <v>27.789746153846156</v>
+      </c>
+      <c r="Y157" s="6">
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="Z157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA157" s="8">
+        <v>7.5166666666666675</v>
+      </c>
+      <c r="AB157" s="8">
+        <v>4.2512846153846153</v>
+      </c>
+      <c r="AC157" s="8">
+        <v>12.483333</v>
+      </c>
+      <c r="AD157" s="8">
+        <v>19.428207692307691</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>0.61538461538461542</v>
+      </c>
       <c r="AF157" s="9"/>
-      <c r="AG157" s="5"/>
+      <c r="AG157" s="5">
+        <v>0</v>
+      </c>
       <c r="AH157" s="10">
         <v>4</v>
       </c>
@@ -21335,7 +21479,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
@@ -21371,25 +21515,61 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="8"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-      <c r="AA158" s="8"/>
-      <c r="AB158" s="8"/>
-      <c r="AC158" s="8"/>
-      <c r="AD158" s="8"/>
-      <c r="AE158" s="6"/>
+      <c r="O158" s="5">
+        <v>2438.25</v>
+      </c>
+      <c r="P158" s="5">
+        <v>2438.25</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>-0.16298780655260481</v>
+      </c>
+      <c r="R158" s="7">
+        <v>22</v>
+      </c>
+      <c r="S158" s="6">
+        <v>-0.33333333333333337</v>
+      </c>
+      <c r="T158" s="6">
+        <v>0.27666014559622681</v>
+      </c>
+      <c r="U158" s="6">
+        <v>-0.00228171844560648</v>
+      </c>
+      <c r="V158" s="6">
+        <v>0.042293243104685734</v>
+      </c>
+      <c r="W158" s="6">
+        <v>-0.0072791961447759663</v>
+      </c>
+      <c r="X158" s="8">
+        <v>31.957938095238099</v>
+      </c>
+      <c r="Y158" s="6">
+        <v>0.61904761904761907</v>
+      </c>
+      <c r="Z158" s="6">
+        <v>0.23809523809523808</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>6.4053045454545448</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>5.4761904761904763</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>11.907935999999999</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>18.854761904761904</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0.5714285714285714</v>
+      </c>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>0</v>
+      </c>
       <c r="AH158" s="10">
         <v>2</v>
       </c>
@@ -22206,7 +22386,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>44</v>
@@ -22242,25 +22422,61 @@
       <c t="s" r="N165" s="4">
         <v>52</v>
       </c>
-      <c r="O165" s="5"/>
-      <c r="P165" s="5"/>
-      <c r="Q165" s="6"/>
-      <c r="R165" s="7"/>
-      <c r="S165" s="6"/>
-      <c r="T165" s="6"/>
-      <c r="U165" s="6"/>
-      <c r="V165" s="6"/>
-      <c r="W165" s="6"/>
-      <c r="X165" s="8"/>
-      <c r="Y165" s="6"/>
-      <c r="Z165" s="6"/>
-      <c r="AA165" s="8"/>
-      <c r="AB165" s="8"/>
-      <c r="AC165" s="8"/>
-      <c r="AD165" s="8"/>
-      <c r="AE165" s="6"/>
+      <c r="O165" s="5">
+        <v>3340.1100000000001</v>
+      </c>
+      <c r="P165" s="5">
+        <v>3340.1100000000001</v>
+      </c>
+      <c r="Q165" s="6">
+        <v>-0.21984836593979473</v>
+      </c>
+      <c r="R165" s="7">
+        <v>33</v>
+      </c>
+      <c r="S165" s="6">
+        <v>-0.3529411764705882</v>
+      </c>
+      <c r="T165" s="6">
+        <v>0.32238866384640025</v>
+      </c>
+      <c r="U165" s="6">
+        <v>0.0029321190020687939</v>
+      </c>
+      <c r="V165" s="6">
+        <v>0.030001257443617126</v>
+      </c>
+      <c r="W165" s="6">
+        <v>-0.0095962408423674664</v>
+      </c>
+      <c r="X165" s="8">
+        <v>22.535418750000002</v>
+      </c>
+      <c r="Y165" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="8">
+        <v>4.8762636363636362</v>
+      </c>
+      <c r="AB165" s="8">
+        <v>1.9645812499999999</v>
+      </c>
+      <c r="AC165" s="8">
+        <v>7.044791</v>
+      </c>
+      <c r="AD165" s="8">
+        <v>13.975</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>1</v>
+      </c>
       <c r="AF165" s="9"/>
-      <c r="AG165" s="5"/>
+      <c r="AG165" s="5">
+        <v>24</v>
+      </c>
       <c r="AH165" s="10">
         <v>3</v>
       </c>
